--- a/data/trans_dic/P1426-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1426-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,44</t>
+          <t>2,08; 4,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,59</t>
+          <t>2,22; 4,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 14,08</t>
+          <t>9,05; 13,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,43</t>
+          <t>2,4; 4,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,02</t>
+          <t>2,61; 4,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 14,22</t>
+          <t>10,69; 14,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,12</t>
+          <t>2,49; 4,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,35</t>
+          <t>2,69; 4,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 13,43</t>
+          <t>10,4; 13,09</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,41</t>
+          <t>0,55; 1,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,58</t>
+          <t>0,61; 1,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,87</t>
+          <t>2,76; 4,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,51</t>
+          <t>0,47; 1,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,96</t>
+          <t>0,91; 2,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,8</t>
+          <t>1,97; 3,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,26</t>
+          <t>0,6; 1,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,56</t>
+          <t>0,85; 1,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,21</t>
+          <t>2,55; 3,45</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,11</t>
+          <t>0,22; 3,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,17</t>
+          <t>0,29; 2,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,31</t>
+          <t>2,33; 5,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,93</t>
+          <t>0,48; 2,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,97</t>
+          <t>0,59; 2,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,65</t>
+          <t>1,93; 3,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,22</t>
+          <t>0,55; 2,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,09</t>
+          <t>0,58; 2,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,92</t>
+          <t>2,42; 3,99</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,07</t>
+          <t>1,16; 2,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,86</t>
+          <t>1,05; 1,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,19</t>
+          <t>4,08; 5,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,35</t>
+          <t>1,43; 2,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,5</t>
+          <t>1,57; 2,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 4,94</t>
+          <t>4,14; 5,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,02</t>
+          <t>1,41; 2,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,09</t>
+          <t>1,43; 2,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 4,88</t>
+          <t>4,27; 5,1</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59830</t>
+          <t>62258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93255</t>
+          <t>100767</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>153085</t>
+          <t>163025</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20008; 43276</t>
+          <t>20256; 43189</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16263; 34600</t>
+          <t>16728; 35402</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49044; 72361</t>
+          <t>52266; 75766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31870; 59279</t>
+          <t>32112; 59158</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26529; 49963</t>
+          <t>26005; 49015</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80915; 107027</t>
+          <t>87772; 115777</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58710; 95269</t>
+          <t>57635; 94335</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45732; 76022</t>
+          <t>47098; 76889</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135100; 170154</t>
+          <t>145479; 182974</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>75995</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49597</t>
+          <t>52966</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>120290</t>
+          <t>128961</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10824; 27677</t>
+          <t>10739; 28852</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12462; 32784</t>
+          <t>12572; 32806</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49099; 88612</t>
+          <t>61402; 91380</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8957; 26412</t>
+          <t>8269; 25316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17459; 38984</t>
+          <t>18108; 40588</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35174; 62607</t>
+          <t>42686; 65765</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22586; 46736</t>
+          <t>22275; 46481</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34727; 63270</t>
+          <t>34360; 61976</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92838; 145122</t>
+          <t>112007; 151797</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22993</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>20082</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39787</t>
+          <t>45271</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1047; 14981</t>
+          <t>1050; 14613</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1573; 11842</t>
+          <t>1570; 12695</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16513; 34320</t>
+          <t>16605; 36847</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2188; 13446</t>
+          <t>2218; 13380</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3877; 16336</t>
+          <t>3221; 16382</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11842; 24093</t>
+          <t>14136; 27267</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5166; 20834</t>
+          <t>5174; 22280</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6926; 22957</t>
+          <t>6375; 22472</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30437; 51252</t>
+          <t>34913; 57702</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153516</t>
+          <t>163442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>159646</t>
+          <t>173815</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>313163</t>
+          <t>337258</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40575; 70700</t>
+          <t>39553; 70745</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36605; 62979</t>
+          <t>35617; 63506</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119926; 179156</t>
+          <t>143652; 187415</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51814; 83619</t>
+          <t>50949; 84039</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55441; 88173</t>
+          <t>55560; 91908</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>131087; 180339</t>
+          <t>154104; 194490</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>95776; 140773</t>
+          <t>98309; 141845</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>99578; 144158</t>
+          <t>99043; 142739</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>267054; 346222</t>
+          <t>309241; 369644</t>
         </is>
       </c>
     </row>
